--- a/data/trans_camb/IP04D$notiene-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Estudios-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 24,54</t>
+          <t>4,95; 24,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 39,46</t>
+          <t>1,08; 42,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 22,95</t>
+          <t>2,78; 23,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 12,76</t>
+          <t>-8,25; 11,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 21,15</t>
+          <t>5,75; 20,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 21,18</t>
+          <t>0,15; 22,47</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,57; 352,58</t>
+          <t>33,32; 394,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 627,88</t>
+          <t>1,92; 636,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 329,39</t>
+          <t>16,23; 353,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 198,34</t>
+          <t>-56,49; 166,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,74; 278,77</t>
+          <t>45,53; 274,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 270,11</t>
+          <t>-3,86; 288,13</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 13,09</t>
+          <t>7,32; 13,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 12,83</t>
+          <t>6,57; 13,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 14,31</t>
+          <t>7,96; 14,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 14,6</t>
+          <t>6,65; 14,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,13</t>
+          <t>8,84; 13,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,77</t>
+          <t>7,48; 12,62</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>164,28; 584,99</t>
+          <t>159,47; 568,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>140,18; 560,92</t>
+          <t>160,71; 552,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156,54; 504,84</t>
+          <t>163,6; 513,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138,74; 513,27</t>
+          <t>130,66; 471,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>193,76; 454,02</t>
+          <t>198,72; 458,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>165,29; 437,25</t>
+          <t>170,33; 426,61</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 8,97</t>
+          <t>0,9; 9,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 12,16</t>
+          <t>2,73; 12,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,38; 15,12</t>
+          <t>6,48; 15,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,61; 19,22</t>
+          <t>7,83; 19,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,08</t>
+          <t>4,82; 10,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 14,81</t>
+          <t>6,76; 14,88</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 539,56</t>
+          <t>-2,66; 549,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,58; 781,79</t>
+          <t>42,22; 682,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>193,22; 3705,15</t>
+          <t>173,99; 3392,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>251,81; 4905,71</t>
+          <t>226,82; 4485,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>114,52; 843,33</t>
+          <t>123,11; 824,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>179,64; 1109,96</t>
+          <t>185,81; 1103,25</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,42</t>
+          <t>6,86; 11,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 13,22</t>
+          <t>6,63; 13,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 13,57</t>
+          <t>8,77; 13,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 13,37</t>
+          <t>6,97; 13,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,07; 11,7</t>
+          <t>8,3; 11,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,02</t>
+          <t>7,39; 12,12</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>134,44; 351,49</t>
+          <t>131,52; 356,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>131,69; 384,74</t>
+          <t>132,09; 387,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>160,84; 444,77</t>
+          <t>170,81; 459,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>139,16; 439,01</t>
+          <t>136,67; 419,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>170,72; 336,73</t>
+          <t>170,81; 343,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>162,36; 344,93</t>
+          <t>159,31; 352,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Estudios-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 24,9</t>
+          <t>3,94; 24,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 42,28</t>
+          <t>2,02; 39,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 23,02</t>
+          <t>2,09; 22,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 11,73</t>
+          <t>-7,15; 12,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 20,59</t>
+          <t>5,96; 20,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 22,47</t>
+          <t>-0,06; 22,79</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,32; 394,33</t>
+          <t>21,23; 355,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 636,06</t>
+          <t>1,51; 658,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,23; 353,36</t>
+          <t>7,71; 338,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,49; 166,07</t>
+          <t>-54,53; 175,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,53; 274,89</t>
+          <t>44,44; 281,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 288,13</t>
+          <t>-2,82; 275,0</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 13,3</t>
+          <t>7,63; 13,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 13,4</t>
+          <t>6,52; 13,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,96; 14,37</t>
+          <t>8,17; 14,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 14,12</t>
+          <t>6,67; 14,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,13</t>
+          <t>8,83; 13,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 12,62</t>
+          <t>7,36; 12,78</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>159,47; 568,63</t>
+          <t>167,55; 613,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160,71; 552,75</t>
+          <t>145,15; 565,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163,6; 513,76</t>
+          <t>156,83; 521,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130,66; 471,88</t>
+          <t>124,95; 482,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>198,72; 458,21</t>
+          <t>199,52; 466,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>170,33; 426,61</t>
+          <t>168,63; 447,43</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,18</t>
+          <t>0,89; 9,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 12,82</t>
+          <t>2,79; 12,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 15,0</t>
+          <t>6,4; 15,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 19,77</t>
+          <t>7,57; 19,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,9</t>
+          <t>4,82; 10,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 14,88</t>
+          <t>6,53; 14,93</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 549,39</t>
+          <t>3,95; 526,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,22; 682,56</t>
+          <t>44,13; 814,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>173,99; 3392,52</t>
+          <t>164,91; 3268,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>226,82; 4485,24</t>
+          <t>201,39; 4453,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>123,11; 824,01</t>
+          <t>119,88; 811,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>185,81; 1103,25</t>
+          <t>175,14; 1134,12</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,6</t>
+          <t>6,72; 11,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,03</t>
+          <t>6,67; 13,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,93</t>
+          <t>8,5; 13,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,23</t>
+          <t>6,85; 12,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,3; 11,87</t>
+          <t>8,01; 11,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,12</t>
+          <t>7,69; 12,04</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>131,52; 356,52</t>
+          <t>120,54; 348,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>132,09; 387,6</t>
+          <t>131,59; 392,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>170,81; 459,94</t>
+          <t>162,79; 406,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136,67; 419,02</t>
+          <t>139,41; 390,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>170,81; 343,78</t>
+          <t>161,02; 338,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>159,31; 352,1</t>
+          <t>152,74; 331,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Estudios-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>14,07</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15,67</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,44</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>2,57</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 24,51</t>
+          <t>1,27; 22,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 39,56</t>
+          <t>-8,61; 11,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 22,86</t>
+          <t>3,39; 24,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 12,38</t>
+          <t>-3,48; 15,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,96; 20,83</t>
+          <t>6,43; 21,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 22,79</t>
+          <t>-4,47; 9,66</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>114,91%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>147,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>164,08%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114,91%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,23; 355,07</t>
+          <t>4,78; 329,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 658,15</t>
+          <t>-64,4; 174,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 338,91</t>
+          <t>16,57; 352,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,53; 175,44</t>
+          <t>-39,6; 230,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,44; 281,56</t>
+          <t>48,74; 278,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 275,0</t>
+          <t>-36,04; 122,03</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,81</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>10,36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,75</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,26</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>9,09</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 13,55</t>
+          <t>8,38; 14,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,04</t>
+          <t>5,84; 12,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,34</t>
+          <t>7,54; 13,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 14,56</t>
+          <t>6,4; 12,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,09</t>
+          <t>8,78; 13,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 12,78</t>
+          <t>6,85; 11,47</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>292,35%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>228,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>319,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>300,85%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>292,35%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>264,11%</t>
+          <t>289,66%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>280,2%</t>
+          <t>255,2%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>167,55; 613,98</t>
+          <t>156,54; 504,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>145,15; 565,67</t>
+          <t>116,56; 429,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156,83; 521,09</t>
+          <t>164,28; 584,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124,95; 482,19</t>
+          <t>137,03; 546,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>199,52; 466,4</t>
+          <t>193,76; 454,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>168,63; 447,43</t>
+          <t>151,35; 395,92</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>4,92</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,49</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,5</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,66</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>9,18</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,03</t>
+          <t>6,38; 15,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 12,78</t>
+          <t>6,68; 16,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 15,4</t>
+          <t>0,52; 8,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 19,22</t>
+          <t>1,71; 11,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,88</t>
+          <t>4,86; 11,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 14,93</t>
+          <t>5,96; 13,06</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>816,96%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>869,45%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>148,14%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>225,54%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>816,96%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>984,52%</t>
+          <t>211,58%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>448,3%</t>
+          <t>401,51%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 526,63</t>
+          <t>193,22; 3705,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,13; 814,7</t>
+          <t>218,69; 4515,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>164,91; 3268,22</t>
+          <t>-1,45; 539,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>201,39; 4453,52</t>
+          <t>14,7; 752,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>119,88; 811,65</t>
+          <t>114,52; 843,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>175,14; 1134,12</t>
+          <t>160,54; 1028,43</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10,97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>9,05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,97</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>8,3</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,38</t>
+          <t>8,2; 13,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 13,28</t>
+          <t>6,01; 11,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,38</t>
+          <t>6,94; 11,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 12,96</t>
+          <t>5,74; 10,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,85</t>
+          <t>8,07; 11,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,04</t>
+          <t>6,44; 10,18</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>270,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>208,47%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>221,73%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>230,94%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>270,05%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>241,68%</t>
+          <t>198,67%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>236,63%</t>
+          <t>203,8%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>120,54; 348,25</t>
+          <t>160,84; 444,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>131,59; 392,9</t>
+          <t>114,47; 361,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162,79; 406,42</t>
+          <t>134,44; 351,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>139,41; 390,79</t>
+          <t>111,25; 327,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>161,02; 338,23</t>
+          <t>170,72; 336,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>152,74; 331,58</t>
+          <t>136,89; 292,25</t>
         </is>
       </c>
     </row>
